--- a/clients/4_Rick_May/Loopbaan onderzoek 5.0 template - filled 20260309-143259.xlsx
+++ b/clients/4_Rick_May/Loopbaan onderzoek 5.0 template - filled 20260309-143259.xlsx
@@ -4776,9 +4776,9 @@
   </sheetData>
   <mergeCells count="221">
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D60:D63"/>
     <mergeCell ref="D53:D55"/>
     <mergeCell ref="E39:E40"/>
+    <mergeCell ref="D60:D63"/>
     <mergeCell ref="F60:F63"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>

--- a/clients/4_Rick_May/Loopbaan onderzoek 5.0 template - filled 20260309-143259.xlsx
+++ b/clients/4_Rick_May/Loopbaan onderzoek 5.0 template - filled 20260309-143259.xlsx
@@ -4776,9 +4776,9 @@
   </sheetData>
   <mergeCells count="221">
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D53:D55"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="D60:D63"/>
+    <mergeCell ref="D53:D55"/>
     <mergeCell ref="F60:F63"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>
